--- a/artfynd/A 14150-2023 artfynd.xlsx
+++ b/artfynd/A 14150-2023 artfynd.xlsx
@@ -804,7 +804,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122680546</v>
+        <v>122680459</v>
       </c>
       <c r="B3" t="n">
         <v>94535</v>
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397614</v>
+        <v>397618</v>
       </c>
       <c r="R3" t="n">
-        <v>6148487</v>
+        <v>6148509</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -936,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122680459</v>
+        <v>122680583</v>
       </c>
       <c r="B4" t="n">
-        <v>94535</v>
+        <v>94741</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,21 +952,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397618</v>
+        <v>397614</v>
       </c>
       <c r="R4" t="n">
-        <v>6148509</v>
+        <v>6148487</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt på grov ek</t>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,10 +1068,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122680583</v>
+        <v>122680629</v>
       </c>
       <c r="B5" t="n">
-        <v>94741</v>
+        <v>103756</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1084,26 +1084,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2667</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1112,13 +1124,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397614</v>
+        <v>397647</v>
       </c>
       <c r="R5" t="n">
-        <v>6148487</v>
+        <v>6148324</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1152,7 +1164,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På grov ek</t>
+          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,22 +1179,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Med ädellövinslag</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1200,10 +1202,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122680629</v>
+        <v>122680587</v>
       </c>
       <c r="B6" t="n">
-        <v>103756</v>
+        <v>85200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1212,43 +1214,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1256,10 +1240,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397647</v>
+        <v>397609</v>
       </c>
       <c r="R6" t="n">
-        <v>6148324</v>
+        <v>6148497</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1294,11 +1278,6 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1309,14 +1288,9 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Med ädellövinslag</t>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Asklågor</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1334,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122680587</v>
+        <v>122680466</v>
       </c>
       <c r="B7" t="n">
-        <v>85200</v>
+        <v>79037</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,20 +1320,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>258917</v>
+        <v>6431</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1372,13 +1351,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397609</v>
+        <v>397618</v>
       </c>
       <c r="R7" t="n">
-        <v>6148497</v>
+        <v>6148509</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1408,6 +1387,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt på ek</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,9 +1404,24 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Asklågor</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1440,14 +1439,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122680466</v>
+        <v>122680546</v>
       </c>
       <c r="B8" t="n">
-        <v>79037</v>
+        <v>94535</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1456,26 +1455,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6431</v>
+        <v>2779</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>397618</v>
+        <v>397614</v>
       </c>
       <c r="R8" t="n">
-        <v>6148509</v>
+        <v>6148487</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt på ek</t>
+          <t>Rikligt på grov ek</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 14150-2023 artfynd.xlsx
+++ b/artfynd/A 14150-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122680606</v>
       </c>
       <c r="B2" t="n">
-        <v>103756</v>
+        <v>103759</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122680459</v>
+        <v>122680629</v>
       </c>
       <c r="B3" t="n">
-        <v>94535</v>
+        <v>103759</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,26 +820,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -848,13 +860,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397618</v>
+        <v>397647</v>
       </c>
       <c r="R3" t="n">
-        <v>6148509</v>
+        <v>6148324</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +900,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt på grov ek</t>
+          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,22 +915,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Med ädellövinslag</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -936,10 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122680583</v>
+        <v>122680466</v>
       </c>
       <c r="B4" t="n">
-        <v>94741</v>
+        <v>79040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,27 +954,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2667</v>
+        <v>6431</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -980,10 +981,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397614</v>
+        <v>397618</v>
       </c>
       <c r="R4" t="n">
-        <v>6148487</v>
+        <v>6148509</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1021,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På grov ek</t>
+          <t>Rikligt på ek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1068,10 +1069,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122680629</v>
+        <v>122680587</v>
       </c>
       <c r="B5" t="n">
-        <v>103756</v>
+        <v>85203</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,43 +1081,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1124,10 +1107,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397647</v>
+        <v>397609</v>
       </c>
       <c r="R5" t="n">
-        <v>6148324</v>
+        <v>6148497</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1162,11 +1145,6 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1177,14 +1155,9 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Med ädellövinslag</t>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Asklågor</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1202,10 +1175,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122680587</v>
+        <v>122680459</v>
       </c>
       <c r="B6" t="n">
-        <v>85200</v>
+        <v>94538</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1214,25 +1187,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>258917</v>
+        <v>2779</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1240,13 +1219,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397609</v>
+        <v>397618</v>
       </c>
       <c r="R6" t="n">
-        <v>6148497</v>
+        <v>6148509</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1276,6 +1255,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt på grov ek</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,9 +1272,24 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Asklågor</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1308,10 +1307,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122680466</v>
+        <v>122680583</v>
       </c>
       <c r="B7" t="n">
-        <v>79037</v>
+        <v>94744</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1324,26 +1323,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6431</v>
+        <v>2667</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1351,10 +1351,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397618</v>
+        <v>397614</v>
       </c>
       <c r="R7" t="n">
-        <v>6148509</v>
+        <v>6148487</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på ek</t>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1442,7 +1442,7 @@
         <v>122680546</v>
       </c>
       <c r="B8" t="n">
-        <v>94535</v>
+        <v>94538</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 14150-2023 artfynd.xlsx
+++ b/artfynd/A 14150-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122680606</v>
+        <v>122680466</v>
       </c>
       <c r="B2" t="n">
-        <v>103759</v>
+        <v>79040</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>6431</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -731,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397648</v>
+        <v>397618</v>
       </c>
       <c r="R2" t="n">
-        <v>6148355</v>
+        <v>6148509</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 21 plantor runt koordinaten. Endast enstaka blommande vilket gjorde det svårt att räkna.</t>
+          <t>Rikligt på ek</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +773,22 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Ädellövsumpskog</t>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122680629</v>
+        <v>122680459</v>
       </c>
       <c r="B3" t="n">
-        <v>103759</v>
+        <v>94538</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,38 +822,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>2779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -860,13 +850,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397647</v>
+        <v>397618</v>
       </c>
       <c r="R3" t="n">
-        <v>6148324</v>
+        <v>6148509</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,7 +890,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
+          <t>Rikligt på grov ek</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,12 +905,22 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Med ädellövinslag</t>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -938,10 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122680466</v>
+        <v>122680583</v>
       </c>
       <c r="B4" t="n">
-        <v>79040</v>
+        <v>94744</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,26 +954,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6431</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -981,10 +982,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397618</v>
+        <v>397614</v>
       </c>
       <c r="R4" t="n">
-        <v>6148509</v>
+        <v>6148487</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1021,7 +1022,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt på ek</t>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122680587</v>
+        <v>122680606</v>
       </c>
       <c r="B5" t="n">
-        <v>85203</v>
+        <v>103759</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,25 +1082,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>258917</v>
+        <v>222412</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1107,10 +1126,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397609</v>
+        <v>397648</v>
       </c>
       <c r="R5" t="n">
-        <v>6148497</v>
+        <v>6148355</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1145,6 +1164,11 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 21 plantor runt koordinaten. Endast enstaka blommande vilket gjorde det svårt att räkna.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1155,9 +1179,9 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Asklågor</t>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Ädellövsumpskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1175,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122680459</v>
+        <v>122680587</v>
       </c>
       <c r="B6" t="n">
-        <v>94538</v>
+        <v>85203</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,31 +1211,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2779</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Guldlockmossa</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>M.Stadler &amp; J.Fourn.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1219,13 +1237,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397618</v>
+        <v>397609</v>
       </c>
       <c r="R6" t="n">
-        <v>6148509</v>
+        <v>6148497</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1255,11 +1273,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt på grov ek</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,24 +1285,9 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Asklågor</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1307,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122680583</v>
+        <v>122680629</v>
       </c>
       <c r="B7" t="n">
-        <v>94744</v>
+        <v>103759</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,26 +1321,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2667</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1351,13 +1361,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397614</v>
+        <v>397647</v>
       </c>
       <c r="R7" t="n">
-        <v>6148487</v>
+        <v>6148324</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1391,7 +1401,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På grov ek</t>
+          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,22 +1416,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Med ädellövinslag</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 14150-2023 artfynd.xlsx
+++ b/artfynd/A 14150-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122680466</v>
+        <v>122680583</v>
       </c>
       <c r="B2" t="n">
-        <v>79040</v>
+        <v>94847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6431</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397618</v>
+        <v>397614</v>
       </c>
       <c r="R2" t="n">
-        <v>6148509</v>
+        <v>6148487</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt på ek</t>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122680459</v>
+        <v>122680629</v>
       </c>
       <c r="B3" t="n">
-        <v>94538</v>
+        <v>103862</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,26 +823,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -850,13 +863,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397618</v>
+        <v>397647</v>
       </c>
       <c r="R3" t="n">
-        <v>6148509</v>
+        <v>6148324</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,7 +903,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt på grov ek</t>
+          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,22 +918,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Med ädellövinslag</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -938,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122680583</v>
+        <v>122680459</v>
       </c>
       <c r="B4" t="n">
-        <v>94744</v>
+        <v>94641</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,21 +957,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -982,10 +985,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397614</v>
+        <v>397618</v>
       </c>
       <c r="R4" t="n">
-        <v>6148487</v>
+        <v>6148509</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1022,7 +1025,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På grov ek</t>
+          <t>Rikligt på grov ek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1073,7 +1076,7 @@
         <v>122680606</v>
       </c>
       <c r="B5" t="n">
-        <v>103759</v>
+        <v>103862</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1199,10 +1202,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122680587</v>
+        <v>122680466</v>
       </c>
       <c r="B6" t="n">
-        <v>85203</v>
+        <v>79142</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,20 +1214,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>258917</v>
+        <v>6431</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1237,13 +1245,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397609</v>
+        <v>397618</v>
       </c>
       <c r="R6" t="n">
-        <v>6148497</v>
+        <v>6148509</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1273,6 +1281,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt på ek</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,9 +1298,24 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Asklågor</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1305,10 +1333,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122680629</v>
+        <v>122680587</v>
       </c>
       <c r="B7" t="n">
-        <v>103759</v>
+        <v>85306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,43 +1345,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1361,10 +1371,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397647</v>
+        <v>397609</v>
       </c>
       <c r="R7" t="n">
-        <v>6148324</v>
+        <v>6148497</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1399,11 +1409,6 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1414,14 +1419,9 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Med ädellövinslag</t>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Asklågor</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1442,7 +1442,7 @@
         <v>122680546</v>
       </c>
       <c r="B8" t="n">
-        <v>94538</v>
+        <v>94641</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 14150-2023 artfynd.xlsx
+++ b/artfynd/A 14150-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122680583</v>
       </c>
       <c r="B2" t="n">
-        <v>94847</v>
+        <v>94855</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122680629</v>
+        <v>122680466</v>
       </c>
       <c r="B3" t="n">
-        <v>103862</v>
+        <v>79146</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,39 +823,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>6431</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -863,13 +850,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397647</v>
+        <v>397618</v>
       </c>
       <c r="R3" t="n">
-        <v>6148324</v>
+        <v>6148509</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -903,7 +890,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
+          <t>Rikligt på ek</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,12 +905,22 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Med ädellövinslag</t>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -941,10 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122680459</v>
+        <v>122680587</v>
       </c>
       <c r="B4" t="n">
-        <v>94641</v>
+        <v>85310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,31 +950,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2779</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Guldlockmossa</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>M.Stadler &amp; J.Fourn.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -985,13 +976,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397618</v>
+        <v>397609</v>
       </c>
       <c r="R4" t="n">
-        <v>6148509</v>
+        <v>6148497</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1021,11 +1012,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt på grov ek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,24 +1024,9 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Asklågor</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1073,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122680606</v>
+        <v>122680629</v>
       </c>
       <c r="B5" t="n">
-        <v>103862</v>
+        <v>103870</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1108,7 +1079,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1129,10 +1100,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397648</v>
+        <v>397647</v>
       </c>
       <c r="R5" t="n">
-        <v>6148355</v>
+        <v>6148324</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1169,7 +1140,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 21 plantor runt koordinaten. Endast enstaka blommande vilket gjorde det svårt att räkna.</t>
+          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,7 +1155,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Ädellövsumpskog</t>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Med ädellövinslag</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1202,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122680466</v>
+        <v>122680606</v>
       </c>
       <c r="B6" t="n">
-        <v>79142</v>
+        <v>103870</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1218,26 +1194,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6431</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1245,13 +1234,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397618</v>
+        <v>397648</v>
       </c>
       <c r="R6" t="n">
-        <v>6148509</v>
+        <v>6148355</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1285,7 +1274,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt på ek</t>
+          <t>Minst 21 plantor runt koordinaten. Endast enstaka blommande vilket gjorde det svårt att räkna.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,22 +1289,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+          <t>Ädellövsumpskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1333,10 +1307,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122680587</v>
+        <v>122680459</v>
       </c>
       <c r="B7" t="n">
-        <v>85306</v>
+        <v>94649</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1345,25 +1319,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>258917</v>
+        <v>2779</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1371,13 +1351,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397609</v>
+        <v>397618</v>
       </c>
       <c r="R7" t="n">
-        <v>6148497</v>
+        <v>6148509</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1407,6 +1387,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt på grov ek</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,9 +1404,24 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Asklågor</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1442,7 +1442,7 @@
         <v>122680546</v>
       </c>
       <c r="B8" t="n">
-        <v>94641</v>
+        <v>94649</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 14150-2023 artfynd.xlsx
+++ b/artfynd/A 14150-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122680583</v>
+        <v>122680587</v>
       </c>
       <c r="B2" t="n">
-        <v>94855</v>
+        <v>85310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2667</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Platt fjädermossa</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>M.Stadler &amp; J.Fourn.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397614</v>
+        <v>397609</v>
       </c>
       <c r="R2" t="n">
-        <v>6148487</v>
+        <v>6148497</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,11 +749,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,24 +761,9 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Asklågor</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122680466</v>
+        <v>122680459</v>
       </c>
       <c r="B3" t="n">
-        <v>79146</v>
+        <v>94649</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,26 +797,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6431</v>
+        <v>2779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -890,7 +865,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt på ek</t>
+          <t>Rikligt på grov ek</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122680587</v>
+        <v>122680583</v>
       </c>
       <c r="B4" t="n">
-        <v>85310</v>
+        <v>94855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,25 +925,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>258917</v>
+        <v>2667</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -976,13 +957,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397609</v>
+        <v>397614</v>
       </c>
       <c r="R4" t="n">
-        <v>6148497</v>
+        <v>6148487</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,6 +993,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,9 +1010,24 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Asklågor</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1044,7 +1045,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122680629</v>
+        <v>122680606</v>
       </c>
       <c r="B5" t="n">
         <v>103870</v>
@@ -1079,7 +1080,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1100,10 +1101,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397647</v>
+        <v>397648</v>
       </c>
       <c r="R5" t="n">
-        <v>6148324</v>
+        <v>6148355</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1140,7 +1141,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
+          <t>Minst 21 plantor runt koordinaten. Endast enstaka blommande vilket gjorde det svårt att räkna.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,12 +1156,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Med ädellövinslag</t>
+          <t>Ädellövsumpskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1178,10 +1174,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122680606</v>
+        <v>122680466</v>
       </c>
       <c r="B6" t="n">
-        <v>103870</v>
+        <v>79146</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1194,39 +1190,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>6431</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1234,13 +1217,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397648</v>
+        <v>397618</v>
       </c>
       <c r="R6" t="n">
-        <v>6148355</v>
+        <v>6148509</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1274,7 +1257,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 21 plantor runt koordinaten. Endast enstaka blommande vilket gjorde det svårt att räkna.</t>
+          <t>Rikligt på ek</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1272,22 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Ädellövsumpskog</t>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1307,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122680459</v>
+        <v>122680629</v>
       </c>
       <c r="B7" t="n">
-        <v>94649</v>
+        <v>103870</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,26 +1321,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2779</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1351,13 +1361,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397618</v>
+        <v>397647</v>
       </c>
       <c r="R7" t="n">
-        <v>6148509</v>
+        <v>6148324</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1391,7 +1401,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på grov ek</t>
+          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,22 +1416,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Med ädellövinslag</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 14150-2023 artfynd.xlsx
+++ b/artfynd/A 14150-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122680587</v>
+        <v>122680606</v>
       </c>
       <c r="B2" t="n">
-        <v>85310</v>
+        <v>103872</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>258917</v>
+        <v>222412</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +731,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397609</v>
+        <v>397648</v>
       </c>
       <c r="R2" t="n">
-        <v>6148497</v>
+        <v>6148355</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,6 +769,11 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Minst 21 plantor runt koordinaten. Endast enstaka blommande vilket gjorde det svårt att räkna.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -761,9 +784,9 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Asklågor</t>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Ädellövsumpskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -781,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122680459</v>
+        <v>122680583</v>
       </c>
       <c r="B3" t="n">
-        <v>94649</v>
+        <v>94857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +820,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +848,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397618</v>
+        <v>397614</v>
       </c>
       <c r="R3" t="n">
-        <v>6148509</v>
+        <v>6148487</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +888,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt på grov ek</t>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +936,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122680583</v>
+        <v>122680629</v>
       </c>
       <c r="B4" t="n">
-        <v>94855</v>
+        <v>103872</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,26 +952,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2667</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -957,13 +992,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397614</v>
+        <v>397647</v>
       </c>
       <c r="R4" t="n">
-        <v>6148487</v>
+        <v>6148324</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +1032,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På grov ek</t>
+          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,22 +1047,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Med ädellövinslag</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1045,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122680606</v>
+        <v>122680459</v>
       </c>
       <c r="B5" t="n">
-        <v>103870</v>
+        <v>94651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1061,38 +1086,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>2779</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1101,13 +1114,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397648</v>
+        <v>397618</v>
       </c>
       <c r="R5" t="n">
-        <v>6148355</v>
+        <v>6148509</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1141,7 +1154,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 21 plantor runt koordinaten. Endast enstaka blommande vilket gjorde det svårt att räkna.</t>
+          <t>Rikligt på grov ek</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,7 +1169,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Ädellövsumpskog</t>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1305,10 +1333,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122680629</v>
+        <v>122680587</v>
       </c>
       <c r="B7" t="n">
-        <v>103870</v>
+        <v>85310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,43 +1345,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1361,10 +1371,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397647</v>
+        <v>397609</v>
       </c>
       <c r="R7" t="n">
-        <v>6148324</v>
+        <v>6148497</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1399,11 +1409,6 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1414,14 +1419,9 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Med ädellövinslag</t>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Asklågor</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1442,7 +1442,7 @@
         <v>122680546</v>
       </c>
       <c r="B8" t="n">
-        <v>94649</v>
+        <v>94651</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 14150-2023 artfynd.xlsx
+++ b/artfynd/A 14150-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122680606</v>
+        <v>122680459</v>
       </c>
       <c r="B2" t="n">
-        <v>103872</v>
+        <v>94651</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>2779</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -731,13 +719,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397648</v>
+        <v>397618</v>
       </c>
       <c r="R2" t="n">
-        <v>6148355</v>
+        <v>6148509</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 21 plantor runt koordinaten. Endast enstaka blommande vilket gjorde det svårt att räkna.</t>
+          <t>Rikligt på grov ek</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +774,22 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Ädellövsumpskog</t>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -1070,10 +1073,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122680459</v>
+        <v>122680606</v>
       </c>
       <c r="B5" t="n">
-        <v>94651</v>
+        <v>103872</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,26 +1089,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2779</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1114,13 +1129,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397618</v>
+        <v>397648</v>
       </c>
       <c r="R5" t="n">
-        <v>6148509</v>
+        <v>6148355</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1154,7 +1169,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt på grov ek</t>
+          <t>Minst 21 plantor runt koordinaten. Endast enstaka blommande vilket gjorde det svårt att räkna.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,22 +1184,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+          <t>Ädellövsumpskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1202,10 +1202,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122680466</v>
+        <v>122680587</v>
       </c>
       <c r="B6" t="n">
-        <v>79146</v>
+        <v>85310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1214,25 +1214,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6431</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lönnlav</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>M.Stadler &amp; J.Fourn.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1245,13 +1240,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397618</v>
+        <v>397609</v>
       </c>
       <c r="R6" t="n">
-        <v>6148509</v>
+        <v>6148497</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1281,11 +1276,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt på ek</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,24 +1288,9 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Asklågor</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1333,10 +1308,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122680587</v>
+        <v>122680466</v>
       </c>
       <c r="B7" t="n">
-        <v>85310</v>
+        <v>79146</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1345,20 +1320,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>258917</v>
+        <v>6431</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lönnlav</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1371,13 +1351,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397609</v>
+        <v>397618</v>
       </c>
       <c r="R7" t="n">
-        <v>6148497</v>
+        <v>6148509</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1407,6 +1387,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt på ek</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,9 +1404,24 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Asklågor</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 14150-2023 artfynd.xlsx
+++ b/artfynd/A 14150-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122680459</v>
+        <v>122680466</v>
       </c>
       <c r="B2" t="n">
-        <v>94651</v>
+        <v>79146</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2779</v>
+        <v>6431</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -759,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt på grov ek</t>
+          <t>Rikligt på ek</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,7 +809,7 @@
         <v>122680583</v>
       </c>
       <c r="B3" t="n">
-        <v>94857</v>
+        <v>94865</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -939,10 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122680629</v>
+        <v>122680606</v>
       </c>
       <c r="B4" t="n">
-        <v>103872</v>
+        <v>103880</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -974,7 +973,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -995,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397647</v>
+        <v>397648</v>
       </c>
       <c r="R4" t="n">
-        <v>6148324</v>
+        <v>6148355</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1035,7 +1034,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
+          <t>Minst 21 plantor runt koordinaten. Endast enstaka blommande vilket gjorde det svårt att räkna.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,12 +1049,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Med ädellövinslag</t>
+          <t>Ädellövsumpskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1073,10 +1067,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122680606</v>
+        <v>122680459</v>
       </c>
       <c r="B5" t="n">
-        <v>103872</v>
+        <v>94659</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1089,38 +1083,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>2779</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Hedw.) Schimp.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1129,13 +1111,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397648</v>
+        <v>397618</v>
       </c>
       <c r="R5" t="n">
-        <v>6148355</v>
+        <v>6148509</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1169,7 +1151,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Minst 21 plantor runt koordinaten. Endast enstaka blommande vilket gjorde det svårt att räkna.</t>
+          <t>Rikligt på grov ek</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,7 +1166,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Ädellövsumpskog</t>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1202,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122680587</v>
+        <v>122680629</v>
       </c>
       <c r="B6" t="n">
-        <v>85310</v>
+        <v>103880</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1214,25 +1211,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>258917</v>
+        <v>222412</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1240,10 +1255,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397609</v>
+        <v>397647</v>
       </c>
       <c r="R6" t="n">
-        <v>6148497</v>
+        <v>6148324</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1278,6 +1293,11 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1288,9 +1308,14 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Asklågor</t>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Med ädellövinslag</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1308,10 +1333,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122680466</v>
+        <v>122680587</v>
       </c>
       <c r="B7" t="n">
-        <v>79146</v>
+        <v>85310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1320,25 +1345,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6431</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Lönnlav</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>M.Stadler &amp; J.Fourn.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1351,13 +1371,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397618</v>
+        <v>397609</v>
       </c>
       <c r="R7" t="n">
-        <v>6148509</v>
+        <v>6148497</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1387,11 +1407,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt på ek</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,24 +1419,9 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Asklågor</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1442,7 +1442,7 @@
         <v>122680546</v>
       </c>
       <c r="B8" t="n">
-        <v>94651</v>
+        <v>94659</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 14150-2023 artfynd.xlsx
+++ b/artfynd/A 14150-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122680466</v>
+        <v>122680583</v>
       </c>
       <c r="B2" t="n">
-        <v>79146</v>
+        <v>94865</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6431</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397618</v>
+        <v>397614</v>
       </c>
       <c r="R2" t="n">
-        <v>6148509</v>
+        <v>6148487</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt på ek</t>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122680583</v>
+        <v>122680459</v>
       </c>
       <c r="B3" t="n">
-        <v>94865</v>
+        <v>94659</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,21 +823,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -850,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397614</v>
+        <v>397618</v>
       </c>
       <c r="R3" t="n">
-        <v>6148487</v>
+        <v>6148509</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +891,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På grov ek</t>
+          <t>Rikligt på grov ek</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1067,10 +1068,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122680459</v>
+        <v>122680587</v>
       </c>
       <c r="B5" t="n">
-        <v>94659</v>
+        <v>85310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1079,31 +1080,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2779</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Guldlockmossa</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>M.Stadler &amp; J.Fourn.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1111,13 +1106,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397618</v>
+        <v>397609</v>
       </c>
       <c r="R5" t="n">
-        <v>6148509</v>
+        <v>6148497</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1147,11 +1142,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt på grov ek</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,24 +1154,9 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Asklågor</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1199,10 +1174,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122680629</v>
+        <v>122680466</v>
       </c>
       <c r="B6" t="n">
-        <v>103880</v>
+        <v>79146</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1215,39 +1190,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>6431</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1255,13 +1217,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397647</v>
+        <v>397618</v>
       </c>
       <c r="R6" t="n">
-        <v>6148324</v>
+        <v>6148509</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1295,7 +1257,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
+          <t>Rikligt på ek</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1310,12 +1272,22 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Med ädellövinslag</t>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1333,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122680587</v>
+        <v>122680629</v>
       </c>
       <c r="B7" t="n">
-        <v>85310</v>
+        <v>103880</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1345,25 +1317,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>258917</v>
+        <v>222412</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1371,10 +1361,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397609</v>
+        <v>397647</v>
       </c>
       <c r="R7" t="n">
-        <v>6148497</v>
+        <v>6148324</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1409,6 +1399,11 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1419,9 +1414,14 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Asklågor</t>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Med ädellövinslag</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 14150-2023 artfynd.xlsx
+++ b/artfynd/A 14150-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122680583</v>
+        <v>122680466</v>
       </c>
       <c r="B2" t="n">
-        <v>94865</v>
+        <v>79146</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2667</v>
+        <v>6431</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397614</v>
+        <v>397618</v>
       </c>
       <c r="R2" t="n">
-        <v>6148487</v>
+        <v>6148509</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På grov ek</t>
+          <t>Rikligt på ek</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1068,10 +1067,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122680587</v>
+        <v>122680629</v>
       </c>
       <c r="B5" t="n">
-        <v>85310</v>
+        <v>103880</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1080,25 +1079,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>258917</v>
+        <v>222412</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1106,10 +1123,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397609</v>
+        <v>397647</v>
       </c>
       <c r="R5" t="n">
-        <v>6148497</v>
+        <v>6148324</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1144,6 +1161,11 @@
           <t>2025-02-19</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1154,9 +1176,14 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Asklågor</t>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Med ädellövinslag</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1174,10 +1201,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122680466</v>
+        <v>122680583</v>
       </c>
       <c r="B6" t="n">
-        <v>79146</v>
+        <v>94865</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,26 +1217,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6431</v>
+        <v>2667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1217,10 +1245,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397618</v>
+        <v>397614</v>
       </c>
       <c r="R6" t="n">
-        <v>6148509</v>
+        <v>6148487</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1257,7 +1285,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt på ek</t>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,10 +1333,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122680629</v>
+        <v>122680587</v>
       </c>
       <c r="B7" t="n">
-        <v>103880</v>
+        <v>85310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,43 +1345,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1361,10 +1371,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397647</v>
+        <v>397609</v>
       </c>
       <c r="R7" t="n">
-        <v>6148324</v>
+        <v>6148497</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1399,11 +1409,6 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1414,14 +1419,9 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Med ädellövinslag</t>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Asklågor</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 14150-2023 artfynd.xlsx
+++ b/artfynd/A 14150-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122680466</v>
+        <v>122680629</v>
       </c>
       <c r="B2" t="n">
-        <v>79146</v>
+        <v>103880</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6431</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,13 +731,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397618</v>
+        <v>397647</v>
       </c>
       <c r="R2" t="n">
-        <v>6148509</v>
+        <v>6148324</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,7 +771,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Rikligt på ek</t>
+          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,22 +786,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Med ädellövinslag</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122680459</v>
+        <v>122680466</v>
       </c>
       <c r="B3" t="n">
-        <v>94659</v>
+        <v>79146</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,27 +825,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2779</v>
+        <v>6431</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -890,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt på grov ek</t>
+          <t>Rikligt på ek</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -938,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122680606</v>
+        <v>122680583</v>
       </c>
       <c r="B4" t="n">
-        <v>103880</v>
+        <v>94865</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,38 +956,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -994,13 +984,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397648</v>
+        <v>397614</v>
       </c>
       <c r="R4" t="n">
-        <v>6148355</v>
+        <v>6148487</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1034,7 +1024,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Minst 21 plantor runt koordinaten. Endast enstaka blommande vilket gjorde det svårt att räkna.</t>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,7 +1039,22 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Ädellövsumpskog</t>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1067,10 +1072,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122680629</v>
+        <v>122680587</v>
       </c>
       <c r="B5" t="n">
-        <v>103880</v>
+        <v>85310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1079,43 +1084,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tibast</t>
-        </is>
+        <v>258917</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hypoxylon petriniae</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>M.Stadler &amp; J.Fourn.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1123,10 +1110,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397647</v>
+        <v>397609</v>
       </c>
       <c r="R5" t="n">
-        <v>6148324</v>
+        <v>6148497</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1161,11 +1148,6 @@
           <t>2025-02-19</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1176,14 +1158,9 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Sumpskog</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Med ädellövinslag</t>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Asklågor</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1201,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122680583</v>
+        <v>122680606</v>
       </c>
       <c r="B6" t="n">
-        <v>94865</v>
+        <v>103880</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,26 +1194,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2667</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1245,13 +1234,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397614</v>
+        <v>397648</v>
       </c>
       <c r="R6" t="n">
-        <v>6148487</v>
+        <v>6148355</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1285,7 +1274,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På grov ek</t>
+          <t>Minst 21 plantor runt koordinaten. Endast enstaka blommande vilket gjorde det svårt att räkna.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,22 +1289,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+          <t>Ädellövsumpskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1333,10 +1307,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122680587</v>
+        <v>122680459</v>
       </c>
       <c r="B7" t="n">
-        <v>85310</v>
+        <v>94659</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1345,25 +1319,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>258917</v>
+        <v>2779</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1371,13 +1351,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397609</v>
+        <v>397618</v>
       </c>
       <c r="R7" t="n">
-        <v>6148497</v>
+        <v>6148509</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1407,6 +1387,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt på grov ek</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,9 +1404,24 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Asklågor</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>

--- a/artfynd/A 14150-2023 artfynd.xlsx
+++ b/artfynd/A 14150-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122680629</v>
+        <v>122680583</v>
       </c>
       <c r="B2" t="n">
-        <v>103880</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>2667</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -731,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>397647</v>
+        <v>397614</v>
       </c>
       <c r="R2" t="n">
-        <v>6148324</v>
+        <v>6148487</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,7 +754,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
+          <t>På grov ek</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,12 +769,22 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Sumpskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Med ädellövinslag</t>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -809,15 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122680466</v>
+        <v>122680445</v>
       </c>
       <c r="B3" t="n">
-        <v>79146</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,26 +813,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6431</v>
+        <v>2779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -852,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>397618</v>
+        <v>397627</v>
       </c>
       <c r="R3" t="n">
-        <v>6148509</v>
+        <v>6148492</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +856,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Svedala</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -877,7 +866,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Börringe</t>
+          <t>Gärdslöv</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -888,11 +877,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-19</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt på ek</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,24 +889,19 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>skogsek</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Quercus robur</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -940,15 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122680583</v>
+        <v>122680459</v>
       </c>
       <c r="B4" t="n">
-        <v>94865</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,21 +930,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2667</v>
+        <v>2779</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -984,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>397614</v>
+        <v>397618</v>
       </c>
       <c r="R4" t="n">
-        <v>6148487</v>
+        <v>6148509</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +998,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På grov ek</t>
+          <t>Rikligt på grov ek</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1072,37 +1046,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122680587</v>
+        <v>122680546</v>
       </c>
       <c r="B5" t="n">
-        <v>85310</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>258917</v>
+        <v>2779</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Guldlockmossa</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hypoxylon petriniae</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M.Stadler &amp; J.Fourn.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1110,13 +1085,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>397609</v>
+        <v>397614</v>
       </c>
       <c r="R5" t="n">
-        <v>6148497</v>
+        <v>6148487</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1146,6 +1121,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt på grov ek</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,9 +1138,24 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Asklågor</t>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1178,15 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122680606</v>
+        <v>122680466</v>
       </c>
       <c r="B6" t="n">
-        <v>103880</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79707</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,39 +1184,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>6431</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>(Hoffm.) A.Massal.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1234,13 +1211,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>397648</v>
+        <v>397618</v>
       </c>
       <c r="R6" t="n">
-        <v>6148355</v>
+        <v>6148509</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1274,7 +1251,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Minst 21 plantor runt koordinaten. Endast enstaka blommande vilket gjorde det svårt att räkna.</t>
+          <t>Rikligt på ek</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1266,22 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Ädellövsumpskog</t>
+          <t>Ädellövskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1307,15 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122680459</v>
+        <v>122680606</v>
       </c>
       <c r="B7" t="n">
-        <v>94659</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1323,26 +1310,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2779</v>
+        <v>222412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1351,13 +1350,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>397618</v>
+        <v>397648</v>
       </c>
       <c r="R7" t="n">
-        <v>6148509</v>
+        <v>6148355</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1391,7 +1390,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt på grov ek</t>
+          <t>Minst 21 plantor runt koordinaten. Endast enstaka blommande vilket gjorde det svårt att räkna.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,22 +1405,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+          <t>Ädellövsumpskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1439,15 +1423,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122680546</v>
+        <v>122680629</v>
       </c>
       <c r="B8" t="n">
-        <v>94659</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>104628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1455,26 +1434,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2779</v>
+        <v>222412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1483,13 +1474,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>397614</v>
+        <v>397647</v>
       </c>
       <c r="R8" t="n">
-        <v>6148487</v>
+        <v>6148324</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1523,7 +1514,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt på grov ek</t>
+          <t>Minst 25 plantor runt koordinaten. Säkert fler - svårt att räkna då endast enstaka blommade.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1538,22 +1529,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Ädellövskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Med ädellövinslag</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 14150-2023 artfynd.xlsx
+++ b/artfynd/A 14150-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122680583</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,6 +926,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122680445</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1043,6 +1058,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122680459</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1170,6 +1190,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122680546</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1296,6 +1321,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122680466</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1420,6 +1450,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122680606</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1549,8 +1584,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122680629</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>